--- a/backend/prisma/seed-data/ppn-in-out.xlsx
+++ b/backend/prisma/seed-data/ppn-in-out.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="24000"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17685"/>
   </bookViews>
   <sheets>
     <sheet name="PPN In and Out" sheetId="51" r:id="rId1"/>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PPN In and Out'!$A$4:$S$360</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1953,10 +1953,10 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="[$-409]mmm\-yy;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="[$-409]mmm\-yy;@"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -2129,8 +2129,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2138,18 +2138,18 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
@@ -2200,10 +2200,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -2212,23 +2212,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2258,7 +2258,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2272,7 +2272,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2618,7 +2618,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A2:Z363"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15.75"/>
   <cols>
@@ -18058,9 +18057,15 @@
         <f>49595169-H274</f>
         <v>11219472</v>
       </c>
-      <c r="I275" s="49"/>
-      <c r="J275" s="49"/>
-      <c r="K275" s="49"/>
+      <c r="I275" s="49">
+        <v>0</v>
+      </c>
+      <c r="J275" s="49">
+        <v>0</v>
+      </c>
+      <c r="K275" s="49">
+        <v>0</v>
+      </c>
       <c r="L275" s="49"/>
       <c r="M275" s="46">
         <f>H275</f>
@@ -19915,10 +19920,18 @@
       <c r="E308" s="22"/>
       <c r="F308" s="22"/>
       <c r="G308" s="14"/>
-      <c r="H308" s="14"/>
-      <c r="I308" s="27"/>
-      <c r="J308" s="27"/>
-      <c r="K308" s="27"/>
+      <c r="H308" s="14">
+        <v>0</v>
+      </c>
+      <c r="I308" s="27">
+        <v>0</v>
+      </c>
+      <c r="J308" s="27">
+        <v>0</v>
+      </c>
+      <c r="K308" s="27">
+        <v>0</v>
+      </c>
       <c r="L308" s="27"/>
       <c r="M308" s="14">
         <v>2200000</v>
@@ -23037,13 +23050,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:S360">
-    <filterColumn colId="15">
-      <filters>
-        <filter val="Inter Accounts"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A4:S360"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
